--- a/docs/Employee Dataset.xlsx
+++ b/docs/Employee Dataset.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\User\Documents\GitHub\data_201_lab_sessions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D919753D-5618-4657-AA0A-E2D9B04E94D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{343C1D2D-7D00-4BE1-BF1C-336015F65BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{7C9ACE7D-7322-4030-98FD-9C0CE6DD86FE}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="65">
   <si>
     <t>Year</t>
   </si>
@@ -152,9 +152,6 @@
   </si>
   <si>
     <t>Apr</t>
-  </si>
-  <si>
-    <t>Type of Worker</t>
   </si>
   <si>
     <t>North</t>
@@ -1084,7 +1081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EFE3B02-3059-4F82-B705-9FA4E156D17D}">
-  <dimension ref="A1:Q101"/>
+  <dimension ref="A1:P101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="7.21875" bestFit="1" customWidth="1"/>
@@ -1096,7 +1093,7 @@
     <col min="17" max="17" width="13.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1145,11 +1142,8 @@
       <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2022</v>
       </c>
@@ -1198,12 +1192,8 @@
       <c r="P2">
         <v>485</v>
       </c>
-      <c r="Q2" t="str">
-        <f>IF(N2="Yes","In-person","Remote")</f>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2023</v>
       </c>
@@ -1252,12 +1242,8 @@
       <c r="P3">
         <v>806</v>
       </c>
-      <c r="Q3" t="str">
-        <f t="shared" ref="Q3:Q66" si="0">IF(N3="Yes","In-person","Remote")</f>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2021</v>
       </c>
@@ -1306,12 +1292,8 @@
       <c r="P4">
         <v>570</v>
       </c>
-      <c r="Q4" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2023</v>
       </c>
@@ -1360,12 +1342,8 @@
       <c r="P5">
         <v>218</v>
       </c>
-      <c r="Q5" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2023</v>
       </c>
@@ -1414,12 +1392,8 @@
       <c r="P6">
         <v>495</v>
       </c>
-      <c r="Q6" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2020</v>
       </c>
@@ -1468,12 +1442,8 @@
       <c r="P7">
         <v>631</v>
       </c>
-      <c r="Q7" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2021</v>
       </c>
@@ -1522,12 +1492,8 @@
       <c r="P8">
         <v>360</v>
       </c>
-      <c r="Q8" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2021</v>
       </c>
@@ -1576,12 +1542,8 @@
       <c r="P9">
         <v>904</v>
       </c>
-      <c r="Q9" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2021</v>
       </c>
@@ -1630,12 +1592,8 @@
       <c r="P10">
         <v>355</v>
       </c>
-      <c r="Q10" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2023</v>
       </c>
@@ -1684,12 +1642,8 @@
       <c r="P11">
         <v>833</v>
       </c>
-      <c r="Q11" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2022</v>
       </c>
@@ -1738,12 +1692,8 @@
       <c r="P12">
         <v>325</v>
       </c>
-      <c r="Q12" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2021</v>
       </c>
@@ -1792,12 +1742,8 @@
       <c r="P13">
         <v>152</v>
       </c>
-      <c r="Q13" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2024</v>
       </c>
@@ -1846,12 +1792,8 @@
       <c r="P14">
         <v>966</v>
       </c>
-      <c r="Q14" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2023</v>
       </c>
@@ -1900,12 +1842,8 @@
       <c r="P15">
         <v>599</v>
       </c>
-      <c r="Q15" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2020</v>
       </c>
@@ -1954,12 +1892,8 @@
       <c r="P16">
         <v>605</v>
       </c>
-      <c r="Q16" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2022</v>
       </c>
@@ -2008,12 +1942,8 @@
       <c r="P17">
         <v>953</v>
       </c>
-      <c r="Q17" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2024</v>
       </c>
@@ -2062,12 +1992,8 @@
       <c r="P18">
         <v>463</v>
       </c>
-      <c r="Q18" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2024</v>
       </c>
@@ -2116,12 +2042,8 @@
       <c r="P19">
         <v>379</v>
       </c>
-      <c r="Q19" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2020</v>
       </c>
@@ -2170,12 +2092,8 @@
       <c r="P20">
         <v>692</v>
       </c>
-      <c r="Q20" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2022</v>
       </c>
@@ -2224,12 +2142,8 @@
       <c r="P21">
         <v>813</v>
       </c>
-      <c r="Q21" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2023</v>
       </c>
@@ -2278,12 +2192,8 @@
       <c r="P22">
         <v>257</v>
       </c>
-      <c r="Q22" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2019</v>
       </c>
@@ -2332,12 +2242,8 @@
       <c r="P23">
         <v>731</v>
       </c>
-      <c r="Q23" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2022</v>
       </c>
@@ -2386,12 +2292,8 @@
       <c r="P24">
         <v>158</v>
       </c>
-      <c r="Q24" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2020</v>
       </c>
@@ -2440,12 +2342,8 @@
       <c r="P25">
         <v>826</v>
       </c>
-      <c r="Q25" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2024</v>
       </c>
@@ -2494,12 +2392,8 @@
       <c r="P26">
         <v>227</v>
       </c>
-      <c r="Q26" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2023</v>
       </c>
@@ -2548,12 +2442,8 @@
       <c r="P27">
         <v>835</v>
       </c>
-      <c r="Q27" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2022</v>
       </c>
@@ -2602,12 +2492,8 @@
       <c r="P28">
         <v>820</v>
       </c>
-      <c r="Q28" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>2019</v>
       </c>
@@ -2656,12 +2542,8 @@
       <c r="P29">
         <v>981</v>
       </c>
-      <c r="Q29" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>2019</v>
       </c>
@@ -2710,12 +2592,8 @@
       <c r="P30">
         <v>214</v>
       </c>
-      <c r="Q30" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>2021</v>
       </c>
@@ -2764,12 +2642,8 @@
       <c r="P31">
         <v>308</v>
       </c>
-      <c r="Q31" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>2021</v>
       </c>
@@ -2818,12 +2692,8 @@
       <c r="P32">
         <v>625</v>
       </c>
-      <c r="Q32" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>2020</v>
       </c>
@@ -2872,12 +2742,8 @@
       <c r="P33">
         <v>620</v>
       </c>
-      <c r="Q33" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>2022</v>
       </c>
@@ -2926,12 +2792,8 @@
       <c r="P34">
         <v>651</v>
       </c>
-      <c r="Q34" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>2022</v>
       </c>
@@ -2980,12 +2842,8 @@
       <c r="P35">
         <v>336</v>
       </c>
-      <c r="Q35" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>2024</v>
       </c>
@@ -3034,12 +2892,8 @@
       <c r="P36">
         <v>380</v>
       </c>
-      <c r="Q36" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>2024</v>
       </c>
@@ -3088,12 +2942,8 @@
       <c r="P37">
         <v>458</v>
       </c>
-      <c r="Q37" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>2024</v>
       </c>
@@ -3142,12 +2992,8 @@
       <c r="P38">
         <v>300</v>
       </c>
-      <c r="Q38" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>2021</v>
       </c>
@@ -3196,12 +3042,8 @@
       <c r="P39">
         <v>857</v>
       </c>
-      <c r="Q39" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>2022</v>
       </c>
@@ -3250,12 +3092,8 @@
       <c r="P40">
         <v>377</v>
       </c>
-      <c r="Q40" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>2022</v>
       </c>
@@ -3304,12 +3142,8 @@
       <c r="P41">
         <v>334</v>
       </c>
-      <c r="Q41" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>2019</v>
       </c>
@@ -3358,12 +3192,8 @@
       <c r="P42">
         <v>593</v>
       </c>
-      <c r="Q42" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>2021</v>
       </c>
@@ -3412,12 +3242,8 @@
       <c r="P43">
         <v>103</v>
       </c>
-      <c r="Q43" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>2023</v>
       </c>
@@ -3466,12 +3292,8 @@
       <c r="P44">
         <v>765</v>
       </c>
-      <c r="Q44" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>2021</v>
       </c>
@@ -3520,12 +3342,8 @@
       <c r="P45">
         <v>541</v>
       </c>
-      <c r="Q45" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>2023</v>
       </c>
@@ -3574,12 +3392,8 @@
       <c r="P46">
         <v>128</v>
       </c>
-      <c r="Q46" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>2019</v>
       </c>
@@ -3628,12 +3442,8 @@
       <c r="P47">
         <v>208</v>
       </c>
-      <c r="Q47" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>2020</v>
       </c>
@@ -3682,12 +3492,8 @@
       <c r="P48">
         <v>709</v>
       </c>
-      <c r="Q48" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>2022</v>
       </c>
@@ -3736,12 +3542,8 @@
       <c r="P49">
         <v>826</v>
       </c>
-      <c r="Q49" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>2019</v>
       </c>
@@ -3790,12 +3592,8 @@
       <c r="P50">
         <v>904</v>
       </c>
-      <c r="Q50" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>2022</v>
       </c>
@@ -3844,12 +3642,8 @@
       <c r="P51">
         <v>174</v>
       </c>
-      <c r="Q51" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>2024</v>
       </c>
@@ -3898,12 +3692,8 @@
       <c r="P52">
         <v>937</v>
       </c>
-      <c r="Q52" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>2020</v>
       </c>
@@ -3952,12 +3742,8 @@
       <c r="P53">
         <v>245</v>
       </c>
-      <c r="Q53" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>2020</v>
       </c>
@@ -4006,12 +3792,8 @@
       <c r="P54">
         <v>227</v>
       </c>
-      <c r="Q54" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>2019</v>
       </c>
@@ -4060,12 +3842,8 @@
       <c r="P55">
         <v>952</v>
       </c>
-      <c r="Q55" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>2020</v>
       </c>
@@ -4114,12 +3892,8 @@
       <c r="P56">
         <v>141</v>
       </c>
-      <c r="Q56" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>2023</v>
       </c>
@@ -4168,12 +3942,8 @@
       <c r="P57">
         <v>455</v>
       </c>
-      <c r="Q57" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>2020</v>
       </c>
@@ -4222,12 +3992,8 @@
       <c r="P58">
         <v>140</v>
       </c>
-      <c r="Q58" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>2022</v>
       </c>
@@ -4276,12 +4042,8 @@
       <c r="P59">
         <v>133</v>
       </c>
-      <c r="Q59" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>2022</v>
       </c>
@@ -4330,12 +4092,8 @@
       <c r="P60">
         <v>116</v>
       </c>
-      <c r="Q60" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>2022</v>
       </c>
@@ -4384,12 +4142,8 @@
       <c r="P61">
         <v>776</v>
       </c>
-      <c r="Q61" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>2022</v>
       </c>
@@ -4438,12 +4192,8 @@
       <c r="P62">
         <v>252</v>
       </c>
-      <c r="Q62" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>2023</v>
       </c>
@@ -4492,12 +4242,8 @@
       <c r="P63">
         <v>477</v>
       </c>
-      <c r="Q63" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>2021</v>
       </c>
@@ -4546,12 +4292,8 @@
       <c r="P64">
         <v>687</v>
       </c>
-      <c r="Q64" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>2024</v>
       </c>
@@ -4600,12 +4342,8 @@
       <c r="P65">
         <v>698</v>
       </c>
-      <c r="Q65" t="str">
-        <f t="shared" si="0"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>2019</v>
       </c>
@@ -4654,12 +4392,8 @@
       <c r="P66">
         <v>728</v>
       </c>
-      <c r="Q66" t="str">
-        <f t="shared" si="0"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>2022</v>
       </c>
@@ -4708,12 +4442,8 @@
       <c r="P67">
         <v>973</v>
       </c>
-      <c r="Q67" t="str">
-        <f t="shared" ref="Q67:Q101" si="1">IF(N67="Yes","In-person","Remote")</f>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>2020</v>
       </c>
@@ -4762,12 +4492,8 @@
       <c r="P68">
         <v>441</v>
       </c>
-      <c r="Q68" t="str">
-        <f t="shared" si="1"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>2022</v>
       </c>
@@ -4816,12 +4542,8 @@
       <c r="P69">
         <v>126</v>
       </c>
-      <c r="Q69" t="str">
-        <f t="shared" si="1"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>2020</v>
       </c>
@@ -4870,12 +4592,8 @@
       <c r="P70">
         <v>924</v>
       </c>
-      <c r="Q70" t="str">
-        <f t="shared" si="1"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>2024</v>
       </c>
@@ -4924,12 +4642,8 @@
       <c r="P71">
         <v>386</v>
       </c>
-      <c r="Q71" t="str">
-        <f t="shared" si="1"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>2024</v>
       </c>
@@ -4978,12 +4692,8 @@
       <c r="P72">
         <v>745</v>
       </c>
-      <c r="Q72" t="str">
-        <f t="shared" si="1"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>2024</v>
       </c>
@@ -5032,12 +4742,8 @@
       <c r="P73">
         <v>830</v>
       </c>
-      <c r="Q73" t="str">
-        <f t="shared" si="1"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>2020</v>
       </c>
@@ -5086,12 +4792,8 @@
       <c r="P74">
         <v>267</v>
       </c>
-      <c r="Q74" t="str">
-        <f t="shared" si="1"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>2022</v>
       </c>
@@ -5140,12 +4842,8 @@
       <c r="P75">
         <v>709</v>
       </c>
-      <c r="Q75" t="str">
-        <f t="shared" si="1"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>2024</v>
       </c>
@@ -5194,12 +4892,8 @@
       <c r="P76">
         <v>367</v>
       </c>
-      <c r="Q76" t="str">
-        <f t="shared" si="1"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>2023</v>
       </c>
@@ -5248,12 +4942,8 @@
       <c r="P77">
         <v>848</v>
       </c>
-      <c r="Q77" t="str">
-        <f t="shared" si="1"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>2020</v>
       </c>
@@ -5302,12 +4992,8 @@
       <c r="P78">
         <v>920</v>
       </c>
-      <c r="Q78" t="str">
-        <f t="shared" si="1"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>2020</v>
       </c>
@@ -5356,12 +5042,8 @@
       <c r="P79">
         <v>554</v>
       </c>
-      <c r="Q79" t="str">
-        <f t="shared" si="1"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>2022</v>
       </c>
@@ -5410,12 +5092,8 @@
       <c r="P80">
         <v>784</v>
       </c>
-      <c r="Q80" t="str">
-        <f t="shared" si="1"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>2020</v>
       </c>
@@ -5464,12 +5142,8 @@
       <c r="P81">
         <v>500</v>
       </c>
-      <c r="Q81" t="str">
-        <f t="shared" si="1"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>2020</v>
       </c>
@@ -5518,12 +5192,8 @@
       <c r="P82">
         <v>575</v>
       </c>
-      <c r="Q82" t="str">
-        <f t="shared" si="1"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>2024</v>
       </c>
@@ -5572,12 +5242,8 @@
       <c r="P83">
         <v>801</v>
       </c>
-      <c r="Q83" t="str">
-        <f t="shared" si="1"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>2022</v>
       </c>
@@ -5626,12 +5292,8 @@
       <c r="P84">
         <v>733</v>
       </c>
-      <c r="Q84" t="str">
-        <f t="shared" si="1"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>2024</v>
       </c>
@@ -5680,12 +5342,8 @@
       <c r="P85">
         <v>657</v>
       </c>
-      <c r="Q85" t="str">
-        <f t="shared" si="1"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>2024</v>
       </c>
@@ -5734,12 +5392,8 @@
       <c r="P86">
         <v>675</v>
       </c>
-      <c r="Q86" t="str">
-        <f t="shared" si="1"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>2022</v>
       </c>
@@ -5788,12 +5442,8 @@
       <c r="P87">
         <v>229</v>
       </c>
-      <c r="Q87" t="str">
-        <f t="shared" si="1"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>2019</v>
       </c>
@@ -5842,12 +5492,8 @@
       <c r="P88">
         <v>921</v>
       </c>
-      <c r="Q88" t="str">
-        <f t="shared" si="1"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>2024</v>
       </c>
@@ -5896,12 +5542,8 @@
       <c r="P89">
         <v>462</v>
       </c>
-      <c r="Q89" t="str">
-        <f t="shared" si="1"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>2023</v>
       </c>
@@ -5950,12 +5592,8 @@
       <c r="P90">
         <v>804</v>
       </c>
-      <c r="Q90" t="str">
-        <f t="shared" si="1"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>2023</v>
       </c>
@@ -6004,12 +5642,8 @@
       <c r="P91">
         <v>918</v>
       </c>
-      <c r="Q91" t="str">
-        <f t="shared" si="1"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>2020</v>
       </c>
@@ -6058,12 +5692,8 @@
       <c r="P92">
         <v>792</v>
       </c>
-      <c r="Q92" t="str">
-        <f t="shared" si="1"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>2023</v>
       </c>
@@ -6112,12 +5742,8 @@
       <c r="P93">
         <v>391</v>
       </c>
-      <c r="Q93" t="str">
-        <f t="shared" si="1"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>2020</v>
       </c>
@@ -6166,12 +5792,8 @@
       <c r="P94">
         <v>470</v>
       </c>
-      <c r="Q94" t="str">
-        <f t="shared" si="1"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>2019</v>
       </c>
@@ -6220,12 +5842,8 @@
       <c r="P95">
         <v>893</v>
       </c>
-      <c r="Q95" t="str">
-        <f t="shared" si="1"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>2022</v>
       </c>
@@ -6274,12 +5892,8 @@
       <c r="P96">
         <v>128</v>
       </c>
-      <c r="Q96" t="str">
-        <f t="shared" si="1"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>2022</v>
       </c>
@@ -6328,12 +5942,8 @@
       <c r="P97">
         <v>248</v>
       </c>
-      <c r="Q97" t="str">
-        <f t="shared" si="1"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>2022</v>
       </c>
@@ -6382,12 +5992,8 @@
       <c r="P98">
         <v>878</v>
       </c>
-      <c r="Q98" t="str">
-        <f t="shared" si="1"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>2023</v>
       </c>
@@ -6436,12 +6042,8 @@
       <c r="P99">
         <v>395</v>
       </c>
-      <c r="Q99" t="str">
-        <f t="shared" si="1"/>
-        <v>Remote</v>
-      </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>2019</v>
       </c>
@@ -6490,12 +6092,8 @@
       <c r="P100">
         <v>110</v>
       </c>
-      <c r="Q100" t="str">
-        <f t="shared" si="1"/>
-        <v>In-person</v>
-      </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>2023</v>
       </c>
@@ -6543,10 +6141,6 @@
       </c>
       <c r="P101">
         <v>611</v>
-      </c>
-      <c r="Q101" t="str">
-        <f t="shared" si="1"/>
-        <v>In-person</v>
       </c>
     </row>
   </sheetData>
@@ -6567,7 +6161,7 @@
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C1" s="3"/>
     </row>
@@ -6576,21 +6170,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="D2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3">
         <v>95</v>
@@ -6607,7 +6201,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -6624,7 +6218,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5">
         <v>120</v>
@@ -6641,7 +6235,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B6">
         <v>115</v>
@@ -6675,7 +6269,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B8">
         <v>85</v>
@@ -6692,7 +6286,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B9">
         <v>135</v>
@@ -6709,7 +6303,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B10">
         <v>110</v>
@@ -6726,7 +6320,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11">
         <v>100</v>
@@ -6743,7 +6337,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B12">
         <v>50</v>
@@ -6760,7 +6354,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B13">
         <v>40</v>
@@ -6777,7 +6371,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B14">
         <v>40</v>
@@ -6808,15 +6402,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B2">
         <v>6</v>
@@ -6824,7 +6418,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B3">
         <v>11</v>
@@ -6832,7 +6426,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B4">
         <v>15</v>
@@ -6840,7 +6434,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B5">
         <v>21</v>
@@ -6848,7 +6442,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>24</v>
@@ -6856,7 +6450,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B7">
         <v>28</v>
@@ -6864,7 +6458,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B8">
         <v>29</v>
@@ -6872,7 +6466,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B9">
         <v>37</v>
